--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/INDIANA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/INDIANA_2013.xlsx
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C170">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C635">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C730">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C885">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1099">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1125">
@@ -22902,7 +22902,7 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1253">
